--- a/review-results/复盘信息抓取-20260801.xlsx
+++ b/review-results/复盘信息抓取-20260801.xlsx
@@ -1044,7 +1044,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1054,7 +1054,7 @@
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
@@ -1112,1046 +1112,3926 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>395.07</v>
+      </c>
       <c r="I2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
+      <c r="L2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>395.07</v>
+      </c>
       <c r="I3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
+      <c r="L3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>392.39</v>
+      </c>
       <c r="I4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
+      <c r="L4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>442.76</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>409</v>
+      </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
+      <c r="L5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>510.79</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>425.23</v>
+      </c>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
+      <c r="L6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>472.45</v>
+      </c>
       <c r="S6" s="3" t="n"/>
       <c r="T6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>510.23</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>423.72</v>
+      </c>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
+      <c r="L7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>472.45</v>
+      </c>
       <c r="S7" s="3" t="n"/>
       <c r="T7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0145</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>510.23</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>424.44</v>
+      </c>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+      <c r="L8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0145</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>472.45</v>
+      </c>
       <c r="S8" s="3" t="n"/>
       <c r="T8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>510.79</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>426.98</v>
+      </c>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
+      <c r="L9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>472.45</v>
+      </c>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>421.98</v>
+      </c>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
+      <c r="L10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0230</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>423.72</v>
+      </c>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
+      <c r="L11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0230</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S11" s="3" t="n"/>
       <c r="T11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>413.47</v>
+      </c>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
+      <c r="L12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>393.76</v>
+      </c>
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
+      <c r="L13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S13" s="3" t="n"/>
       <c r="T13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>392.51</v>
+      </c>
       <c r="I14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
+      <c r="L14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S14" s="3" t="n"/>
       <c r="T14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>391.07</v>
+      </c>
       <c r="I15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
+      <c r="L15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S15" s="3" t="n"/>
       <c r="T15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>373.13</v>
+      </c>
       <c r="I16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
+      <c r="L16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S16" s="3" t="n"/>
       <c r="T16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0400</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>370.29</v>
+      </c>
       <c r="I17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
+      <c r="L17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0400</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S17" s="3" t="n"/>
       <c r="T17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0415</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>373.54</v>
+      </c>
       <c r="I18" s="3" t="n"/>
-      <c r="M18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
+      <c r="L18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0415</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S18" s="3" t="n"/>
       <c r="T18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0430</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>365.17</v>
+      </c>
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
+      <c r="L19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0430</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S19" s="3" t="n"/>
       <c r="T19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0445</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>364.98</v>
+      </c>
       <c r="H20" s="3" t="n"/>
       <c r="I20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="O20" s="3" t="n"/>
+      <c r="L20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0445</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0500</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>365.69</v>
+      </c>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
+      <c r="L21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0500</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S21" s="3" t="n"/>
       <c r="T21" s="3" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0515</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>366.79</v>
+      </c>
       <c r="H22" s="3" t="n"/>
       <c r="I22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="O22" s="3" t="n"/>
+      <c r="L22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0515</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S22" s="3" t="n"/>
       <c r="T22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>442.76</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>367.04</v>
+      </c>
       <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="O23" s="3" t="n"/>
+      <c r="L23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0545</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>442.76</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>371.22</v>
+      </c>
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="O24" s="3" t="n"/>
+      <c r="L24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0545</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S24" s="3" t="n"/>
       <c r="T24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0600</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>442.76</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>376.95</v>
+      </c>
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
+      <c r="L25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0600</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S25" s="3" t="n"/>
       <c r="T25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0615</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>425.57</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>375.72</v>
+      </c>
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
+      <c r="L26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0615</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S26" s="3" t="n"/>
       <c r="T26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0630</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>382.48</v>
+      </c>
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
+      <c r="L27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0630</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S27" s="3" t="n"/>
       <c r="T27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0645</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>376.95</v>
+      </c>
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
-      <c r="O28" s="3" t="n"/>
+      <c r="L28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0645</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S28" s="3" t="n"/>
       <c r="T28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>363.57</v>
+      </c>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
-      <c r="O29" s="3" t="n"/>
+      <c r="L29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S29" s="3" t="n"/>
       <c r="T29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>393.8</v>
+      </c>
       <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="O30" s="3" t="n"/>
+      <c r="L30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>484.33</v>
+      </c>
       <c r="S30" s="3" t="n"/>
       <c r="T30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>360.29</v>
+      </c>
       <c r="H31" s="3" t="n"/>
       <c r="I31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
+      <c r="L31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>484.33</v>
+      </c>
       <c r="S31" s="3" t="n"/>
       <c r="T31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0745</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>342.3</v>
+      </c>
       <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
+      <c r="L32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0745</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>484.33</v>
+      </c>
       <c r="S32" s="3" t="n"/>
       <c r="T32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>339.04</v>
+      </c>
       <c r="H33" s="3" t="n"/>
       <c r="I33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
+      <c r="L33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>484.33</v>
+      </c>
       <c r="S33" s="3" t="n"/>
       <c r="T33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0815</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>337.14</v>
+      </c>
       <c r="H34" s="3" t="n"/>
       <c r="I34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="O34" s="3" t="n"/>
+      <c r="L34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0815</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>461.7</v>
+      </c>
       <c r="S34" s="3" t="n"/>
       <c r="T34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>393.35</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>339.04</v>
+      </c>
       <c r="H35" s="3" t="n"/>
       <c r="I35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="O35" s="3" t="n"/>
+      <c r="L35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>462.45</v>
+      </c>
       <c r="S35" s="3" t="n"/>
       <c r="T35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>393.35</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>339.48</v>
+      </c>
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n"/>
-      <c r="M36" s="3" t="n"/>
-      <c r="O36" s="3" t="n"/>
+      <c r="L36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>462.45</v>
+      </c>
       <c r="S36" s="3" t="n"/>
       <c r="T36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0900</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>337.01</v>
+      </c>
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n"/>
-      <c r="M37" s="3" t="n"/>
-      <c r="O37" s="3" t="n"/>
+      <c r="L37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0900</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>469.79</v>
+      </c>
       <c r="S37" s="3" t="n"/>
       <c r="T37" s="3" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>339.86</v>
+      </c>
       <c r="H38" s="3" t="n"/>
       <c r="I38" s="3" t="n"/>
-      <c r="M38" s="3" t="n"/>
-      <c r="O38" s="3" t="n"/>
+      <c r="L38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>443.3</v>
+      </c>
       <c r="S38" s="3" t="n"/>
       <c r="T38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n"/>
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0930</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>341.23</v>
+      </c>
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
-      <c r="O39" s="3" t="n"/>
+      <c r="L39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0930</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>443.3</v>
+      </c>
       <c r="S39" s="3" t="n"/>
       <c r="T39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0945</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>339.14</v>
+      </c>
       <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n"/>
-      <c r="M40" s="3" t="n"/>
-      <c r="O40" s="3" t="n"/>
+      <c r="L40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0945</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>443.3</v>
+      </c>
       <c r="S40" s="3" t="n"/>
       <c r="T40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>340.47</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>337.01</v>
+      </c>
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
-      <c r="M41" s="3" t="n"/>
-      <c r="O41" s="3" t="n"/>
+      <c r="L41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>443.3</v>
+      </c>
       <c r="S41" s="3" t="n"/>
       <c r="T41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="n"/>
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>340.47</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>339.04</v>
+      </c>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
-      <c r="M42" s="3" t="n"/>
-      <c r="O42" s="3" t="n"/>
+      <c r="L42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>443.3</v>
+      </c>
       <c r="S42" s="3" t="n"/>
       <c r="T42" s="3" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n"/>
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>339.3</v>
+      </c>
       <c r="H43" s="3" t="n"/>
       <c r="I43" s="3" t="n"/>
-      <c r="M43" s="3" t="n"/>
-      <c r="O43" s="3" t="n"/>
+      <c r="L43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>443.3</v>
+      </c>
       <c r="S43" s="3" t="n"/>
       <c r="T43" s="3" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="3" t="n"/>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="n"/>
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>343.25</v>
+      </c>
       <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="n"/>
-      <c r="M44" s="3" t="n"/>
-      <c r="O44" s="3" t="n"/>
+      <c r="L44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>439.72</v>
+      </c>
       <c r="S44" s="3" t="n"/>
       <c r="T44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>339.3</v>
+      </c>
       <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="n"/>
-      <c r="M45" s="3" t="n"/>
-      <c r="O45" s="3" t="n"/>
+      <c r="L45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>439.72</v>
+      </c>
       <c r="S45" s="3" t="n"/>
       <c r="T45" s="3" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>336.79</v>
+      </c>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n"/>
-      <c r="M46" s="3" t="n"/>
-      <c r="O46" s="3" t="n"/>
+      <c r="L46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>472.45</v>
+      </c>
       <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>343.25</v>
+      </c>
       <c r="H47" s="3" t="n"/>
       <c r="I47" s="3" t="n"/>
-      <c r="M47" s="3" t="n"/>
-      <c r="O47" s="3" t="n"/>
+      <c r="L47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>472.45</v>
+      </c>
       <c r="S47" s="3" t="n"/>
       <c r="T47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
-      <c r="E48" s="3" t="n"/>
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>391.79</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>350.7</v>
+      </c>
       <c r="H48" s="3" t="n"/>
       <c r="I48" s="3" t="n"/>
-      <c r="M48" s="3" t="n"/>
-      <c r="O48" s="3" t="n"/>
+      <c r="L48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>472.45</v>
+      </c>
       <c r="S48" s="3" t="n"/>
       <c r="T48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>365.39</v>
+      </c>
       <c r="H49" s="3" t="n"/>
       <c r="I49" s="3" t="n"/>
-      <c r="M49" s="3" t="n"/>
-      <c r="O49" s="3" t="n"/>
+      <c r="L49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>472.45</v>
+      </c>
       <c r="S49" s="3" t="n"/>
       <c r="T49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
-      <c r="E50" s="3" t="n"/>
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>390.14</v>
+      </c>
       <c r="H50" s="3" t="n"/>
       <c r="I50" s="3" t="n"/>
-      <c r="M50" s="3" t="n"/>
-      <c r="O50" s="3" t="n"/>
+      <c r="L50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S50" s="3" t="n"/>
       <c r="T50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="n"/>
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>390.14</v>
+      </c>
       <c r="H51" s="3" t="n"/>
       <c r="I51" s="3" t="n"/>
-      <c r="M51" s="3" t="n"/>
-      <c r="O51" s="3" t="n"/>
+      <c r="L51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>501.11</v>
+      </c>
       <c r="S51" s="3" t="n"/>
       <c r="T51" s="3" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="3" t="n"/>
-      <c r="D52" s="3" t="n"/>
-      <c r="E52" s="3" t="n"/>
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>376.95</v>
+      </c>
       <c r="H52" s="3" t="n"/>
       <c r="I52" s="3" t="n"/>
-      <c r="M52" s="3" t="n"/>
-      <c r="O52" s="3" t="n"/>
+      <c r="L52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S52" s="3" t="n"/>
       <c r="T52" s="3" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n"/>
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>367.01</v>
+      </c>
       <c r="H53" s="3" t="n"/>
       <c r="I53" s="3" t="n"/>
-      <c r="M53" s="3" t="n"/>
-      <c r="O53" s="3" t="n"/>
+      <c r="L53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S53" s="3" t="n"/>
       <c r="T53" s="3" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="3" t="n"/>
-      <c r="D54" s="3" t="n"/>
-      <c r="E54" s="3" t="n"/>
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>366.16</v>
+      </c>
       <c r="H54" s="3" t="n"/>
       <c r="I54" s="3" t="n"/>
-      <c r="M54" s="3" t="n"/>
-      <c r="O54" s="3" t="n"/>
+      <c r="L54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>501.11</v>
+      </c>
       <c r="S54" s="3" t="n"/>
       <c r="T54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="3" t="n"/>
-      <c r="D55" s="3" t="n"/>
-      <c r="E55" s="3" t="n"/>
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>403.27</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>391.42</v>
+      </c>
       <c r="H55" s="3" t="n"/>
       <c r="I55" s="3" t="n"/>
-      <c r="M55" s="3" t="n"/>
-      <c r="O55" s="3" t="n"/>
+      <c r="L55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>501.11</v>
+      </c>
       <c r="S55" s="3" t="n"/>
       <c r="T55" s="3" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="3" t="n"/>
-      <c r="D56" s="3" t="n"/>
-      <c r="E56" s="3" t="n"/>
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>403.27</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>390.01</v>
+      </c>
       <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="n"/>
-      <c r="M56" s="3" t="n"/>
-      <c r="O56" s="3" t="n"/>
+      <c r="L56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>501.11</v>
+      </c>
       <c r="S56" s="3" t="n"/>
       <c r="T56" s="3" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="3" t="n"/>
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>403.27</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>391.42</v>
+      </c>
       <c r="H57" s="3" t="n"/>
       <c r="I57" s="3" t="n"/>
-      <c r="M57" s="3" t="n"/>
-      <c r="O57" s="3" t="n"/>
+      <c r="L57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="n">
+        <v>501.11</v>
+      </c>
       <c r="S57" s="3" t="n"/>
       <c r="T57" s="3" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
-      <c r="E58" s="3" t="n"/>
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>393.35</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>409</v>
+      </c>
       <c r="H58" s="3" t="n"/>
       <c r="I58" s="3" t="n"/>
-      <c r="M58" s="3" t="n"/>
-      <c r="O58" s="3" t="n"/>
+      <c r="L58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S58" s="3" t="n"/>
       <c r="T58" s="3" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="3" t="n"/>
-      <c r="D59" s="3" t="n"/>
-      <c r="E59" s="3" t="n"/>
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>390.01</v>
+      </c>
       <c r="H59" s="3" t="n"/>
       <c r="I59" s="3" t="n"/>
-      <c r="M59" s="3" t="n"/>
-      <c r="O59" s="3" t="n"/>
+      <c r="L59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S59" s="3" t="n"/>
       <c r="T59" s="3" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="3" t="n"/>
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>381.36</v>
+      </c>
       <c r="H60" s="3" t="n"/>
       <c r="I60" s="3" t="n"/>
-      <c r="M60" s="3" t="n"/>
-      <c r="O60" s="3" t="n"/>
+      <c r="L60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="n">
+        <v>483.64</v>
+      </c>
       <c r="S60" s="3" t="n"/>
       <c r="T60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n"/>
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>417.76</v>
+      </c>
       <c r="H61" s="3" t="n"/>
       <c r="I61" s="3" t="n"/>
-      <c r="M61" s="3" t="n"/>
-      <c r="O61" s="3" t="n"/>
+      <c r="L61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>483.64</v>
+      </c>
       <c r="S61" s="3" t="n"/>
       <c r="T61" s="3" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="3" t="n"/>
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>400.57</v>
+      </c>
       <c r="H62" s="3" t="n"/>
       <c r="I62" s="3" t="n"/>
-      <c r="M62" s="3" t="n"/>
-      <c r="O62" s="3" t="n"/>
+      <c r="L62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S62" s="3" t="n"/>
       <c r="T62" s="3" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="n"/>
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>445.3</v>
+      </c>
       <c r="H63" s="3" t="n"/>
       <c r="I63" s="3" t="n"/>
-      <c r="M63" s="3" t="n"/>
-      <c r="O63" s="3" t="n"/>
+      <c r="L63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S63" s="3" t="n"/>
       <c r="T63" s="3" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="3" t="n"/>
-      <c r="D64" s="3" t="n"/>
-      <c r="E64" s="3" t="n"/>
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>422.1</v>
+      </c>
       <c r="H64" s="3" t="n"/>
       <c r="I64" s="3" t="n"/>
-      <c r="M64" s="3" t="n"/>
-      <c r="O64" s="3" t="n"/>
+      <c r="L64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S64" s="3" t="n"/>
       <c r="T64" s="3" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
-      <c r="E65" s="3" t="n"/>
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>425.85</v>
+      </c>
       <c r="H65" s="3" t="n"/>
       <c r="I65" s="3" t="n"/>
-      <c r="M65" s="3" t="n"/>
-      <c r="O65" s="3" t="n"/>
+      <c r="L65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S65" s="3" t="n"/>
       <c r="T65" s="3" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="3" t="n"/>
-      <c r="D66" s="3" t="n"/>
-      <c r="E66" s="3" t="n"/>
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1615</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>425.57</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>441.32</v>
+      </c>
       <c r="H66" s="3" t="n"/>
       <c r="I66" s="3" t="n"/>
-      <c r="M66" s="3" t="n"/>
-      <c r="O66" s="3" t="n"/>
+      <c r="L66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>1615</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>501.11</v>
+      </c>
       <c r="S66" s="3" t="n"/>
       <c r="T66" s="3" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="3" t="n"/>
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>445.3</v>
+      </c>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="3" t="n"/>
-      <c r="M67" s="3" t="n"/>
-      <c r="O67" s="3" t="n"/>
+      <c r="L67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>501.11</v>
+      </c>
       <c r="S67" s="3" t="n"/>
       <c r="T67" s="3" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>459.5</v>
+      </c>
       <c r="H68" s="3" t="n"/>
       <c r="I68" s="3" t="n"/>
-      <c r="M68" s="3" t="n"/>
-      <c r="O68" s="3" t="n"/>
+      <c r="L68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="n">
+        <v>501.11</v>
+      </c>
       <c r="S68" s="3" t="n"/>
       <c r="T68" s="3" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="3" t="n"/>
-      <c r="D69" s="3" t="n"/>
-      <c r="E69" s="3" t="n"/>
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>467.95</v>
+      </c>
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="3" t="n"/>
-      <c r="M69" s="3" t="n"/>
-      <c r="O69" s="3" t="n"/>
+      <c r="L69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="n">
+        <v>501.11</v>
+      </c>
       <c r="S69" s="3" t="n"/>
       <c r="T69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="3" t="n"/>
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>483.58</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>473.29</v>
+      </c>
       <c r="H70" s="3" t="n"/>
       <c r="I70" s="3" t="n"/>
-      <c r="M70" s="3" t="n"/>
-      <c r="O70" s="3" t="n"/>
+      <c r="L70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S70" s="3" t="n"/>
       <c r="T70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="3" t="n"/>
-      <c r="D71" s="3" t="n"/>
-      <c r="E71" s="3" t="n"/>
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>483.58</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>473.29</v>
+      </c>
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="3" t="n"/>
-      <c r="M71" s="3" t="n"/>
-      <c r="O71" s="3" t="n"/>
+      <c r="L71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S71" s="3" t="n"/>
       <c r="T71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>483.58</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>480.39</v>
+      </c>
       <c r="H72" s="3" t="n"/>
       <c r="I72" s="3" t="n"/>
-      <c r="M72" s="3" t="n"/>
-      <c r="O72" s="3" t="n"/>
+      <c r="L72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S72" s="3" t="n"/>
       <c r="T72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
-      <c r="E73" s="3" t="n"/>
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>483.58</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>472.39</v>
+      </c>
       <c r="H73" s="3" t="n"/>
       <c r="I73" s="3" t="n"/>
-      <c r="M73" s="3" t="n"/>
-      <c r="O73" s="3" t="n"/>
+      <c r="L73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S73" s="3" t="n"/>
       <c r="T73" s="3" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>410.89</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>473.17</v>
+      </c>
       <c r="H74" s="3" t="n"/>
       <c r="I74" s="3" t="n"/>
-      <c r="M74" s="3" t="n"/>
-      <c r="O74" s="3" t="n"/>
+      <c r="L74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S74" s="3" t="n"/>
       <c r="T74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="B75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>410.89</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>473.77</v>
+      </c>
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="3" t="n"/>
-      <c r="M75" s="3" t="n"/>
-      <c r="O75" s="3" t="n"/>
+      <c r="L75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S75" s="3" t="n"/>
       <c r="T75" s="3" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1845</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>410.89</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>483.1</v>
+      </c>
       <c r="H76" s="3" t="n"/>
       <c r="I76" s="3" t="n"/>
-      <c r="M76" s="3" t="n"/>
-      <c r="O76" s="3" t="n"/>
+      <c r="L76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>1845</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S76" s="3" t="n"/>
       <c r="T76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="3" t="n"/>
-      <c r="D77" s="3" t="n"/>
-      <c r="E77" s="3" t="n"/>
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>410.89</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>484.19</v>
+      </c>
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="3" t="n"/>
-      <c r="M77" s="3" t="n"/>
-      <c r="O77" s="3" t="n"/>
+      <c r="L77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S77" s="3" t="n"/>
       <c r="T77" s="3" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
-      <c r="E78" s="3" t="n"/>
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>425.57</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>481.48</v>
+      </c>
       <c r="H78" s="3" t="n"/>
       <c r="I78" s="3" t="n"/>
-      <c r="M78" s="3" t="n"/>
-      <c r="O78" s="3" t="n"/>
+      <c r="L78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S78" s="3" t="n"/>
       <c r="T78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" s="3" t="n"/>
-      <c r="D79" s="3" t="n"/>
-      <c r="E79" s="3" t="n"/>
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>425.57</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>479.27</v>
+      </c>
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="3" t="n"/>
-      <c r="M79" s="3" t="n"/>
-      <c r="O79" s="3" t="n"/>
+      <c r="L79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S79" s="3" t="n"/>
       <c r="T79" s="3" t="n"/>
     </row>
     <row r="80">
-      <c r="B80" s="3" t="n"/>
-      <c r="D80" s="3" t="n"/>
-      <c r="E80" s="3" t="n"/>
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>425.57</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>478.67</v>
+      </c>
       <c r="H80" s="3" t="n"/>
       <c r="I80" s="3" t="n"/>
-      <c r="M80" s="3" t="n"/>
-      <c r="O80" s="3" t="n"/>
+      <c r="L80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S80" s="3" t="n"/>
       <c r="T80" s="3" t="n"/>
     </row>
     <row r="81">
-      <c r="B81" s="3" t="n"/>
-      <c r="D81" s="3" t="n"/>
-      <c r="E81" s="3" t="n"/>
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>425.57</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>471.55</v>
+      </c>
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="3" t="n"/>
-      <c r="M81" s="3" t="n"/>
-      <c r="O81" s="3" t="n"/>
+      <c r="L81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="O81" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S81" s="3" t="n"/>
       <c r="T81" s="3" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" s="3" t="n"/>
-      <c r="D82" s="3" t="n"/>
-      <c r="E82" s="3" t="n"/>
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>469.44</v>
+      </c>
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="3" t="n"/>
-      <c r="M82" s="3" t="n"/>
-      <c r="O82" s="3" t="n"/>
+      <c r="L82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S82" s="3" t="n"/>
       <c r="T82" s="3" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" s="3" t="n"/>
-      <c r="D83" s="3" t="n"/>
-      <c r="E83" s="3" t="n"/>
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>470.57</v>
+      </c>
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="3" t="n"/>
-      <c r="M83" s="3" t="n"/>
-      <c r="O83" s="3" t="n"/>
+      <c r="L83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S83" s="3" t="n"/>
       <c r="T83" s="3" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" s="3" t="n"/>
-      <c r="D84" s="3" t="n"/>
-      <c r="E84" s="3" t="n"/>
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>466.54</v>
+      </c>
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="3" t="n"/>
-      <c r="M84" s="3" t="n"/>
-      <c r="O84" s="3" t="n"/>
+      <c r="L84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S84" s="3" t="n"/>
       <c r="T84" s="3" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" s="3" t="n"/>
-      <c r="D85" s="3" t="n"/>
-      <c r="E85" s="3" t="n"/>
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>468.14</v>
+      </c>
       <c r="H85" s="3" t="n"/>
       <c r="I85" s="3" t="n"/>
-      <c r="M85" s="3" t="n"/>
-      <c r="O85" s="3" t="n"/>
+      <c r="L85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S85" s="3" t="n"/>
       <c r="T85" s="3" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="3" t="n"/>
-      <c r="D86" s="3" t="n"/>
-      <c r="E86" s="3" t="n"/>
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>425.57</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>461.54</v>
+      </c>
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="3" t="n"/>
-      <c r="M86" s="3" t="n"/>
-      <c r="O86" s="3" t="n"/>
+      <c r="L86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S86" s="3" t="n"/>
       <c r="T86" s="3" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="3" t="n"/>
-      <c r="D87" s="3" t="n"/>
-      <c r="E87" s="3" t="n"/>
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2130</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>425.57</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>467.95</v>
+      </c>
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="3" t="n"/>
-      <c r="M87" s="3" t="n"/>
-      <c r="O87" s="3" t="n"/>
+      <c r="L87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>2130</t>
+        </is>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S87" s="3" t="n"/>
       <c r="T87" s="3" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="3" t="n"/>
-      <c r="D88" s="3" t="n"/>
-      <c r="E88" s="3" t="n"/>
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>469.29</v>
+      </c>
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="3" t="n"/>
-      <c r="M88" s="3" t="n"/>
-      <c r="O88" s="3" t="n"/>
+      <c r="L88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S88" s="3" t="n"/>
       <c r="T88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>421.97</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>472.92</v>
+      </c>
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="3" t="n"/>
-      <c r="M89" s="3" t="n"/>
-      <c r="O89" s="3" t="n"/>
+      <c r="L89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>497.2</v>
+      </c>
       <c r="S89" s="3" t="n"/>
       <c r="T89" s="3" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="3" t="n"/>
-      <c r="D90" s="3" t="n"/>
-      <c r="E90" s="3" t="n"/>
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>466.85</v>
+      </c>
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="3" t="n"/>
-      <c r="M90" s="3" t="n"/>
-      <c r="O90" s="3" t="n"/>
+      <c r="L90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S90" s="3" t="n"/>
       <c r="T90" s="3" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="3" t="n"/>
-      <c r="D91" s="3" t="n"/>
-      <c r="E91" s="3" t="n"/>
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2230</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>460.42</v>
+      </c>
       <c r="H91" s="3" t="n"/>
       <c r="I91" s="3" t="n"/>
-      <c r="M91" s="3" t="n"/>
-      <c r="O91" s="3" t="n"/>
+      <c r="L91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>2230</t>
+        </is>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S91" s="3" t="n"/>
       <c r="T91" s="3" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="3" t="n"/>
-      <c r="D92" s="3" t="n"/>
-      <c r="E92" s="3" t="n"/>
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2245</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>455.89</v>
+      </c>
       <c r="H92" s="3" t="n"/>
       <c r="I92" s="3" t="n"/>
-      <c r="M92" s="3" t="n"/>
-      <c r="O92" s="3" t="n"/>
+      <c r="L92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>2245</t>
+        </is>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S92" s="3" t="n"/>
       <c r="T92" s="3" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="3" t="n"/>
-      <c r="D93" s="3" t="n"/>
-      <c r="E93" s="3" t="n"/>
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>452.67</v>
+      </c>
       <c r="I93" s="3" t="n"/>
-      <c r="M93" s="3" t="n"/>
-      <c r="O93" s="3" t="n"/>
+      <c r="L93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>507.79</v>
+      </c>
       <c r="S93" s="3" t="n"/>
       <c r="T93" s="3" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="3" t="n"/>
-      <c r="D94" s="3" t="n"/>
-      <c r="E94" s="3" t="n"/>
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>442.82</v>
+      </c>
       <c r="I94" s="3" t="n"/>
-      <c r="M94" s="3" t="n"/>
-      <c r="O94" s="3" t="n"/>
+      <c r="L94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="n">
+        <v>509.13</v>
+      </c>
       <c r="S94" s="3" t="n"/>
       <c r="T94" s="3" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="3" t="n"/>
-      <c r="D95" s="3" t="n"/>
-      <c r="E95" s="3" t="n"/>
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>433.57</v>
+      </c>
       <c r="I95" s="3" t="n"/>
-      <c r="M95" s="3" t="n"/>
-      <c r="O95" s="3" t="n"/>
+      <c r="L95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="O95" s="3" t="n">
+        <v>509.13</v>
+      </c>
       <c r="S95" s="3" t="n"/>
       <c r="T95" s="3" t="n"/>
     </row>
     <row r="96">
-      <c r="B96" s="3" t="n"/>
-      <c r="D96" s="3" t="n"/>
-      <c r="E96" s="3" t="n"/>
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>438.83</v>
+      </c>
       <c r="I96" s="3" t="n"/>
-      <c r="M96" s="3" t="n"/>
-      <c r="O96" s="3" t="n"/>
+      <c r="L96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="O96" s="3" t="n">
+        <v>509.13</v>
+      </c>
       <c r="S96" s="3" t="n"/>
       <c r="T96" s="3" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="3" t="n"/>
-      <c r="D97" s="3" t="n"/>
-      <c r="E97" s="3" t="n"/>
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>434.85</v>
+      </c>
       <c r="H97" s="3" t="n"/>
       <c r="I97" s="3" t="n"/>
-      <c r="M97" s="3" t="n"/>
-      <c r="O97" s="3" t="n"/>
+      <c r="L97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="O97" s="3" t="n">
+        <v>509.13</v>
+      </c>
       <c r="S97" s="3" t="n"/>
       <c r="T97" s="3" t="n"/>
     </row>
@@ -12752,8 +15632,12 @@
           <t>00:15</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
+      <c r="C2" s="3" t="n">
+        <v>35191.2</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>9955.77</v>
+      </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
@@ -12775,8 +15659,12 @@
           <t>00:30</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
+      <c r="C3" s="3" t="n">
+        <v>34898.3</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>9774.190000000001</v>
+      </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
@@ -12798,8 +15686,12 @@
           <t>00:45</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
+      <c r="C4" s="3" t="n">
+        <v>34623</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>9292.709999999999</v>
+      </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
@@ -12821,8 +15713,12 @@
           <t>01:00</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
+        <v>34576.9</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>8940.459999999999</v>
+      </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
@@ -12844,8 +15740,12 @@
           <t>01:15</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
+      <c r="C6" s="3" t="n">
+        <v>36679.3</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>9338.540000000001</v>
+      </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
@@ -12867,8 +15767,12 @@
           <t>01:30</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
+      <c r="C7" s="3" t="n">
+        <v>36672.4</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>9335.700000000001</v>
+      </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
@@ -12890,8 +15794,12 @@
           <t>01:45</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
+      <c r="C8" s="3" t="n">
+        <v>36223.7</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>9362.129999999999</v>
+      </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
@@ -12913,8 +15821,12 @@
           <t>02:00</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
+      <c r="C9" s="3" t="n">
+        <v>35246</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>8988.299999999999</v>
+      </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
@@ -12936,8 +15848,12 @@
           <t>02:15</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
+      <c r="C10" s="3" t="n">
+        <v>34700.2</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>8865.030000000001</v>
+      </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
@@ -12959,8 +15875,12 @@
           <t>02:30</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
+      <c r="C11" s="3" t="n">
+        <v>34209.9</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>8710.620000000001</v>
+      </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
@@ -12982,8 +15902,12 @@
           <t>02:45</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
+      <c r="C12" s="3" t="n">
+        <v>33664.4</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>8555.610000000001</v>
+      </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
@@ -13005,8 +15929,12 @@
           <t>03:00</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
+      <c r="C13" s="3" t="n">
+        <v>33661.9</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>8250.530000000001</v>
+      </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
@@ -13028,8 +15956,12 @@
           <t>03:15</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
+      <c r="C14" s="3" t="n">
+        <v>33196.1</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>8096.01</v>
+      </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
@@ -13051,8 +15983,12 @@
           <t>03:30</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
+      <c r="C15" s="3" t="n">
+        <v>32838.9</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>8090.55</v>
+      </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
@@ -13074,8 +16010,12 @@
           <t>03:45</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
+      <c r="C16" s="3" t="n">
+        <v>32568.3</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>8084.11</v>
+      </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
@@ -13097,8 +16037,12 @@
           <t>04:00</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
+      <c r="C17" s="3" t="n">
+        <v>32136.7</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>8077.25</v>
+      </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
       </c>
@@ -13120,8 +16064,12 @@
           <t>04:15</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
+      <c r="C18" s="3" t="n">
+        <v>31941.1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>8082.88</v>
+      </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
       </c>
@@ -13143,8 +16091,12 @@
           <t>04:30</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
+      <c r="C19" s="3" t="n">
+        <v>31782.7</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>8075.39</v>
+      </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
       </c>
@@ -13166,8 +16118,12 @@
           <t>04:45</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
+      <c r="C20" s="3" t="n">
+        <v>31951.4</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>7915.66</v>
+      </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
@@ -13189,8 +16145,12 @@
           <t>05:00</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
+      <c r="C21" s="3" t="n">
+        <v>31926.8</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>7755.86</v>
+      </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
@@ -13212,8 +16172,12 @@
           <t>05:15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
+      <c r="C22" s="3" t="n">
+        <v>31853.9</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>7743.28</v>
+      </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
@@ -13235,8 +16199,12 @@
           <t>05:30</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
+      <c r="C23" s="3" t="n">
+        <v>32238.6</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>7738.16</v>
+      </c>
       <c r="E23" s="3" t="n">
         <v>17.6</v>
       </c>
@@ -13258,8 +16226,12 @@
           <t>05:45</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
+      <c r="C24" s="3" t="n">
+        <v>32472.1</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>7738.03</v>
+      </c>
       <c r="E24" s="3" t="n">
         <v>129.9</v>
       </c>
@@ -13281,8 +16253,12 @@
           <t>06:00</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="C25" s="3" t="n">
+        <v>32527.1</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>7737.66</v>
+      </c>
       <c r="E25" s="3" t="n">
         <v>395.9</v>
       </c>
@@ -13304,8 +16280,12 @@
           <t>06:15</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
+      <c r="C26" s="3" t="n">
+        <v>32809.7</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>7731.22</v>
+      </c>
       <c r="E26" s="3" t="n">
         <v>680.1</v>
       </c>
@@ -13327,8 +16307,12 @@
           <t>06:30</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
+      <c r="C27" s="3" t="n">
+        <v>32624.9</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>7741.99</v>
+      </c>
       <c r="E27" s="3" t="n">
         <v>1042.3</v>
       </c>
@@ -13350,8 +16334,12 @@
           <t>06:45</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="C28" s="3" t="n">
+        <v>32363.8</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>7749.16</v>
+      </c>
       <c r="E28" s="3" t="n">
         <v>1477.2</v>
       </c>
@@ -13373,8 +16361,12 @@
           <t>07:00</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
+      <c r="C29" s="3" t="n">
+        <v>31998.3</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>7520.17</v>
+      </c>
       <c r="E29" s="3" t="n">
         <v>2099.6</v>
       </c>
@@ -13396,8 +16388,12 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
+      <c r="C30" s="3" t="n">
+        <v>31548.9</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>7293.69</v>
+      </c>
       <c r="E30" s="3" t="n">
         <v>2633.2</v>
       </c>
@@ -13419,8 +16415,12 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
+      <c r="C31" s="3" t="n">
+        <v>31652.8</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>6521.36</v>
+      </c>
       <c r="E31" s="3" t="n">
         <v>3248.5</v>
       </c>
@@ -13442,8 +16442,12 @@
           <t>07:45</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
+      <c r="C32" s="3" t="n">
+        <v>31742.5</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>5666.08</v>
+      </c>
       <c r="E32" s="3" t="n">
         <v>3805.7</v>
       </c>
@@ -13465,8 +16469,12 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
+      <c r="C33" s="3" t="n">
+        <v>31934.7</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>4955.21</v>
+      </c>
       <c r="E33" s="3" t="n">
         <v>4487.2</v>
       </c>
@@ -13488,8 +16496,12 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
+      <c r="C34" s="3" t="n">
+        <v>32523.8</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>4972.27</v>
+      </c>
       <c r="E34" s="3" t="n">
         <v>5304.1</v>
       </c>
@@ -13511,8 +16523,12 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
+      <c r="C35" s="3" t="n">
+        <v>32907</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>4971</v>
+      </c>
       <c r="E35" s="3" t="n">
         <v>5871.8</v>
       </c>
@@ -13534,8 +16550,12 @@
           <t>08:45</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
+      <c r="C36" s="3" t="n">
+        <v>33145.3</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>4688.02</v>
+      </c>
       <c r="E36" s="3" t="n">
         <v>6477.4</v>
       </c>
@@ -13557,8 +16577,12 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
+      <c r="C37" s="3" t="n">
+        <v>33693</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>4402.06</v>
+      </c>
       <c r="E37" s="3" t="n">
         <v>6706.8</v>
       </c>
@@ -13580,8 +16604,12 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
+      <c r="C38" s="3" t="n">
+        <v>34217</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>4417.33</v>
+      </c>
       <c r="E38" s="3" t="n">
         <v>7010</v>
       </c>
@@ -13603,8 +16631,12 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
+      <c r="C39" s="3" t="n">
+        <v>34462.7</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>4449.42</v>
+      </c>
       <c r="E39" s="3" t="n">
         <v>7397.7</v>
       </c>
@@ -13626,8 +16658,12 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
+      <c r="C40" s="3" t="n">
+        <v>34741.6</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>4471.09</v>
+      </c>
       <c r="E40" s="3" t="n">
         <v>7844.6</v>
       </c>
@@ -13649,8 +16685,12 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
+      <c r="C41" s="3" t="n">
+        <v>34906.1</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>4482.54</v>
+      </c>
       <c r="E41" s="3" t="n">
         <v>8397.4</v>
       </c>
@@ -13672,8 +16712,12 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
+      <c r="C42" s="3" t="n">
+        <v>35381</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>4502.51</v>
+      </c>
       <c r="E42" s="3" t="n">
         <v>9060.700000000001</v>
       </c>
@@ -13695,8 +16739,12 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
+      <c r="C43" s="3" t="n">
+        <v>35778.4</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>4514.64</v>
+      </c>
       <c r="E43" s="3" t="n">
         <v>9501.799999999999</v>
       </c>
@@ -13718,8 +16766,12 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n"/>
+      <c r="C44" s="3" t="n">
+        <v>36115.8</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>4527.74</v>
+      </c>
       <c r="E44" s="3" t="n">
         <v>9604.9</v>
       </c>
@@ -13741,8 +16793,12 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
+      <c r="C45" s="3" t="n">
+        <v>36755.1</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>4537.07</v>
+      </c>
       <c r="E45" s="3" t="n">
         <v>9637.9</v>
       </c>
@@ -13764,8 +16820,12 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
+      <c r="C46" s="3" t="n">
+        <v>37788.8</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>4535.7</v>
+      </c>
       <c r="E46" s="3" t="n">
         <v>9924.200000000001</v>
       </c>
@@ -13787,8 +16847,12 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
+      <c r="C47" s="3" t="n">
+        <v>37914.2</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>4551.61</v>
+      </c>
       <c r="E47" s="3" t="n">
         <v>9834.9</v>
       </c>
@@ -13810,8 +16874,12 @@
           <t>11:45</t>
         </is>
       </c>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
+      <c r="C48" s="3" t="n">
+        <v>37902.5</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>4546.14</v>
+      </c>
       <c r="E48" s="3" t="n">
         <v>10131.8</v>
       </c>
@@ -13833,8 +16901,12 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
+      <c r="C49" s="3" t="n">
+        <v>37398.4</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>4543.85</v>
+      </c>
       <c r="E49" s="3" t="n">
         <v>9944</v>
       </c>
@@ -13856,8 +16928,12 @@
           <t>12:15</t>
         </is>
       </c>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
+      <c r="C50" s="3" t="n">
+        <v>39733.7</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>5155.06</v>
+      </c>
       <c r="E50" s="3" t="n">
         <v>10094.8</v>
       </c>
@@ -13879,8 +16955,12 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
+      <c r="C51" s="3" t="n">
+        <v>39682.5</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>5746.47</v>
+      </c>
       <c r="E51" s="3" t="n">
         <v>9963.700000000001</v>
       </c>
@@ -13902,8 +16982,12 @@
           <t>12:45</t>
         </is>
       </c>
-      <c r="C52" s="3" t="n"/>
-      <c r="D52" s="3" t="n"/>
+      <c r="C52" s="3" t="n">
+        <v>39799.4</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>6361.24</v>
+      </c>
       <c r="E52" s="3" t="n">
         <v>9927.799999999999</v>
       </c>
@@ -13925,8 +17009,12 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
+      <c r="C53" s="3" t="n">
+        <v>39357.1</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>6958.55</v>
+      </c>
       <c r="E53" s="3" t="n">
         <v>10254.4</v>
       </c>
@@ -13948,8 +17036,12 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="C54" s="3" t="n"/>
-      <c r="D54" s="3" t="n"/>
+      <c r="C54" s="3" t="n">
+        <v>39344.2</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>7550.1</v>
+      </c>
       <c r="E54" s="3" t="n">
         <v>10032.6</v>
       </c>
@@ -13971,8 +17063,12 @@
           <t>13:30</t>
         </is>
       </c>
-      <c r="C55" s="3" t="n"/>
-      <c r="D55" s="3" t="n"/>
+      <c r="C55" s="3" t="n">
+        <v>38945.9</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>8148.18</v>
+      </c>
       <c r="E55" s="3" t="n">
         <v>9948.799999999999</v>
       </c>
@@ -13994,8 +17090,12 @@
           <t>13:45</t>
         </is>
       </c>
-      <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="n"/>
+      <c r="C56" s="3" t="n">
+        <v>39013.1</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>8816.370000000001</v>
+      </c>
       <c r="E56" s="3" t="n">
         <v>9815.200000000001</v>
       </c>
@@ -14017,8 +17117,12 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
+      <c r="C57" s="3" t="n">
+        <v>38185.9</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>9066.77</v>
+      </c>
       <c r="E57" s="3" t="n">
         <v>10032</v>
       </c>
@@ -14040,8 +17144,12 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
+      <c r="C58" s="3" t="n">
+        <v>37890.1</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>9309.52</v>
+      </c>
       <c r="E58" s="3" t="n">
         <v>9517.700000000001</v>
       </c>
@@ -14063,8 +17171,12 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="C59" s="3" t="n"/>
-      <c r="D59" s="3" t="n"/>
+      <c r="C59" s="3" t="n">
+        <v>38179.1</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>9555.809999999999</v>
+      </c>
       <c r="E59" s="3" t="n">
         <v>9125.299999999999</v>
       </c>
@@ -14086,8 +17198,12 @@
           <t>14:45</t>
         </is>
       </c>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
+      <c r="C60" s="3" t="n">
+        <v>38447.8</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>9554.049999999999</v>
+      </c>
       <c r="E60" s="3" t="n">
         <v>8808.700000000001</v>
       </c>
@@ -14109,8 +17225,12 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
+      <c r="C61" s="3" t="n">
+        <v>38913.4</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>9737.35</v>
+      </c>
       <c r="E61" s="3" t="n">
         <v>8372.4</v>
       </c>
@@ -14132,8 +17252,12 @@
           <t>15:15</t>
         </is>
       </c>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
+      <c r="C62" s="3" t="n">
+        <v>38902.3</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>10221.02</v>
+      </c>
       <c r="E62" s="3" t="n">
         <v>8165.2</v>
       </c>
@@ -14155,8 +17279,12 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
+      <c r="C63" s="3" t="n">
+        <v>39340.4</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>10708.03</v>
+      </c>
       <c r="E63" s="3" t="n">
         <v>7672.8</v>
       </c>
@@ -14178,8 +17306,12 @@
           <t>15:45</t>
         </is>
       </c>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="n"/>
+      <c r="C64" s="3" t="n">
+        <v>39943.8</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>10889.93</v>
+      </c>
       <c r="E64" s="3" t="n">
         <v>7138</v>
       </c>
@@ -14201,8 +17333,12 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
+      <c r="C65" s="3" t="n">
+        <v>40166.6</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>10868.84</v>
+      </c>
       <c r="E65" s="3" t="n">
         <v>6109.6</v>
       </c>
@@ -14224,8 +17360,12 @@
           <t>16:15</t>
         </is>
       </c>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="n"/>
+      <c r="C66" s="3" t="n">
+        <v>40591.8</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>10844.6</v>
+      </c>
       <c r="E66" s="3" t="n">
         <v>5466.9</v>
       </c>
@@ -14247,8 +17387,12 @@
           <t>16:30</t>
         </is>
       </c>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
+      <c r="C67" s="3" t="n">
+        <v>41268.5</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>10965.26</v>
+      </c>
       <c r="E67" s="3" t="n">
         <v>4729.5</v>
       </c>
@@ -14270,8 +17414,12 @@
           <t>16:45</t>
         </is>
       </c>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
+      <c r="C68" s="3" t="n">
+        <v>42185</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>11089.83</v>
+      </c>
       <c r="E68" s="3" t="n">
         <v>4124.5</v>
       </c>
@@ -14293,8 +17441,12 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="n"/>
+      <c r="C69" s="3" t="n">
+        <v>43313.4</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>11058.23</v>
+      </c>
       <c r="E69" s="3" t="n">
         <v>3471.9</v>
       </c>
@@ -14316,8 +17468,12 @@
           <t>17:15</t>
         </is>
       </c>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
+      <c r="C70" s="3" t="n">
+        <v>44187.8</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>11026.45</v>
+      </c>
       <c r="E70" s="3" t="n">
         <v>2857.3</v>
       </c>
@@ -14339,8 +17495,12 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="C71" s="3" t="n"/>
-      <c r="D71" s="3" t="n"/>
+      <c r="C71" s="3" t="n">
+        <v>44974.7</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>10999.3</v>
+      </c>
       <c r="E71" s="3" t="n">
         <v>2276.6</v>
       </c>
@@ -14362,8 +17522,12 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
+      <c r="C72" s="3" t="n">
+        <v>45789.8</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>11118.33</v>
+      </c>
       <c r="E72" s="3" t="n">
         <v>1792.8</v>
       </c>
@@ -14385,8 +17549,12 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
+      <c r="C73" s="3" t="n">
+        <v>46345.1</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>11343.74</v>
+      </c>
       <c r="E73" s="3" t="n">
         <v>1333.7</v>
       </c>
@@ -14408,8 +17576,12 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
+      <c r="C74" s="3" t="n">
+        <v>46803.8</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>11579.45</v>
+      </c>
       <c r="E74" s="3" t="n">
         <v>989.5</v>
       </c>
@@ -14431,8 +17603,12 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
+      <c r="C75" s="3" t="n">
+        <v>46926.5</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>11818.18</v>
+      </c>
       <c r="E75" s="3" t="n">
         <v>635.8</v>
       </c>
@@ -14454,8 +17630,12 @@
           <t>18:45</t>
         </is>
       </c>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
+      <c r="C76" s="3" t="n">
+        <v>47183.9</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>11913.27</v>
+      </c>
       <c r="E76" s="3" t="n">
         <v>353.3</v>
       </c>
@@ -14477,8 +17657,12 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="C77" s="3" t="n"/>
-      <c r="D77" s="3" t="n"/>
+      <c r="C77" s="3" t="n">
+        <v>47159</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>11910.67</v>
+      </c>
       <c r="E77" s="3" t="n">
         <v>131.4</v>
       </c>
@@ -14500,8 +17684,12 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="C78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
+      <c r="C78" s="3" t="n">
+        <v>46978.3</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>11915.53</v>
+      </c>
       <c r="E78" s="3" t="n">
         <v>17.6</v>
       </c>
@@ -14523,8 +17711,12 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="C79" s="3" t="n"/>
-      <c r="D79" s="3" t="n"/>
+      <c r="C79" s="3" t="n">
+        <v>47230</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>11920.99</v>
+      </c>
       <c r="E79" s="3" t="n">
         <v>0</v>
       </c>
@@ -14546,8 +17738,12 @@
           <t>19:45</t>
         </is>
       </c>
-      <c r="C80" s="3" t="n"/>
-      <c r="D80" s="3" t="n"/>
+      <c r="C80" s="3" t="n">
+        <v>46930</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>11929.41</v>
+      </c>
       <c r="E80" s="3" t="n">
         <v>0</v>
       </c>
@@ -14569,8 +17765,12 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="C81" s="3" t="n"/>
-      <c r="D81" s="3" t="n"/>
+      <c r="C81" s="3" t="n">
+        <v>46950.2</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>11939.23</v>
+      </c>
       <c r="E81" s="3" t="n">
         <v>0</v>
       </c>
@@ -14592,8 +17792,12 @@
           <t>20:15</t>
         </is>
       </c>
-      <c r="C82" s="3" t="n"/>
-      <c r="D82" s="3" t="n"/>
+      <c r="C82" s="3" t="n">
+        <v>47015.3</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>11940</v>
+      </c>
       <c r="E82" s="3" t="n">
         <v>0</v>
       </c>
@@ -14615,8 +17819,12 @@
           <t>20:30</t>
         </is>
       </c>
-      <c r="C83" s="3" t="n"/>
-      <c r="D83" s="3" t="n"/>
+      <c r="C83" s="3" t="n">
+        <v>46493.3</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>11890.63</v>
+      </c>
       <c r="E83" s="3" t="n">
         <v>0</v>
       </c>
@@ -14638,8 +17846,12 @@
           <t>20:45</t>
         </is>
       </c>
-      <c r="C84" s="3" t="n"/>
-      <c r="D84" s="3" t="n"/>
+      <c r="C84" s="3" t="n">
+        <v>46649.8</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>11840.42</v>
+      </c>
       <c r="E84" s="3" t="n">
         <v>0</v>
       </c>
@@ -14661,8 +17873,12 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="C85" s="3" t="n"/>
-      <c r="D85" s="3" t="n"/>
+      <c r="C85" s="3" t="n">
+        <v>46152.5</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>11789.18</v>
+      </c>
       <c r="E85" s="3" t="n">
         <v>0</v>
       </c>
@@ -14684,8 +17900,12 @@
           <t>21:15</t>
         </is>
       </c>
-      <c r="C86" s="3" t="n"/>
-      <c r="D86" s="3" t="n"/>
+      <c r="C86" s="3" t="n">
+        <v>45903.2</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>11751.52</v>
+      </c>
       <c r="E86" s="3" t="n">
         <v>0</v>
       </c>
@@ -14707,8 +17927,12 @@
           <t>21:30</t>
         </is>
       </c>
-      <c r="C87" s="3" t="n"/>
-      <c r="D87" s="3" t="n"/>
+      <c r="C87" s="3" t="n">
+        <v>45432.1</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>11750.02</v>
+      </c>
       <c r="E87" s="3" t="n">
         <v>0</v>
       </c>
@@ -14730,8 +17954,12 @@
           <t>21:45</t>
         </is>
       </c>
-      <c r="C88" s="3" t="n"/>
-      <c r="D88" s="3" t="n"/>
+      <c r="C88" s="3" t="n">
+        <v>44977.2</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>11646.84</v>
+      </c>
       <c r="E88" s="3" t="n">
         <v>0</v>
       </c>
@@ -14753,8 +17981,12 @@
           <t>22:00</t>
         </is>
       </c>
-      <c r="C89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
+      <c r="C89" s="3" t="n">
+        <v>44438.8</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>11392.75</v>
+      </c>
       <c r="E89" s="3" t="n">
         <v>0</v>
       </c>
@@ -14776,8 +18008,12 @@
           <t>22:15</t>
         </is>
       </c>
-      <c r="C90" s="3" t="n"/>
-      <c r="D90" s="3" t="n"/>
+      <c r="C90" s="3" t="n">
+        <v>43699.3</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>11137.08</v>
+      </c>
       <c r="E90" s="3" t="n">
         <v>0</v>
       </c>
@@ -14799,8 +18035,12 @@
           <t>22:30</t>
         </is>
       </c>
-      <c r="C91" s="3" t="n"/>
-      <c r="D91" s="3" t="n"/>
+      <c r="C91" s="3" t="n">
+        <v>43080.2</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>10731.75</v>
+      </c>
       <c r="E91" s="3" t="n">
         <v>0</v>
       </c>
@@ -14822,8 +18062,12 @@
           <t>22:45</t>
         </is>
       </c>
-      <c r="C92" s="3" t="n"/>
-      <c r="D92" s="3" t="n"/>
+      <c r="C92" s="3" t="n">
+        <v>42205.6</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>10426.8</v>
+      </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
       </c>
@@ -14845,8 +18089,12 @@
           <t>23:00</t>
         </is>
       </c>
-      <c r="C93" s="3" t="n"/>
-      <c r="D93" s="3" t="n"/>
+      <c r="C93" s="3" t="n">
+        <v>41356.4</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>10222.33</v>
+      </c>
       <c r="E93" s="3" t="n">
         <v>0</v>
       </c>
@@ -14868,8 +18116,12 @@
           <t>23:15</t>
         </is>
       </c>
-      <c r="C94" s="3" t="n"/>
-      <c r="D94" s="3" t="n"/>
+      <c r="C94" s="3" t="n">
+        <v>40520.3</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>10018.11</v>
+      </c>
       <c r="E94" s="3" t="n">
         <v>0</v>
       </c>
@@ -14891,8 +18143,12 @@
           <t>23:30</t>
         </is>
       </c>
-      <c r="C95" s="3" t="n"/>
-      <c r="D95" s="3" t="n"/>
+      <c r="C95" s="3" t="n">
+        <v>39664.3</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>9816.389999999999</v>
+      </c>
       <c r="E95" s="3" t="n">
         <v>0</v>
       </c>
@@ -14914,8 +18170,12 @@
           <t>23:45</t>
         </is>
       </c>
-      <c r="C96" s="3" t="n"/>
-      <c r="D96" s="3" t="n"/>
+      <c r="C96" s="3" t="n">
+        <v>38768.3</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>9615.459999999999</v>
+      </c>
       <c r="E96" s="3" t="n">
         <v>0</v>
       </c>
@@ -14937,8 +18197,12 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C97" s="3" t="n"/>
-      <c r="D97" s="3" t="n"/>
+      <c r="C97" s="3" t="n">
+        <v>38425.1</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>9533.48</v>
+      </c>
       <c r="E97" s="3" t="n">
         <v>0</v>
       </c>
@@ -15027,7 +18291,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>日前非市场化机组总出力</t>
+          <t>新能源实际发电曲线</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -15053,7 +18317,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>新能源实际发电曲线</t>
+          <t>省间联络线输电情况</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -15066,53 +18330,53 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>实际系统负荷</t>
+          <t>各时段各类电源电量</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>960</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>省间联络线输电情况</t>
+          <t>各时段各类电源的开机台数</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>768</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>各时段各类电源电量</t>
+          <t>实时储能充电计划及电价</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>960</v>
+        <v>96</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>各时段各类电源的开机台数</t>
+          <t>日前储能充电计划及电价</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>768</v>
+        <v>96</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/review-results/复盘信息抓取-20260801.xlsx
+++ b/review-results/复盘信息抓取-20260801.xlsx
@@ -1043,20 +1043,20 @@
   <dimension ref="A1:T97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
@@ -5049,17 +5049,15 @@
   <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="2"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="7"/>
-    <col width="22" customWidth="1" min="8" max="9"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="8" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6184,33 +6182,31 @@
   <dimension ref="A1:AB97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="24"/>
-    <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="8" customWidth="1" min="25" max="26"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="24"/>
+    <col width="5" customWidth="1" min="25" max="26"/>
+    <col width="6" customWidth="1" min="27" max="27"/>
+    <col width="7" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15576,12 +15572,11 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="6"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18227,9 +18222,9 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
